--- a/feedback_forms/005_decision_analysis_feedback_form--feedback_forms.xlsx
+++ b/feedback_forms/005_decision_analysis_feedback_form--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -853,8 +853,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -882,12 +882,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'marketing'}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Marketing'}</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'sales'}</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Sales'}</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'it'}</t>
+          <t>it</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'IT'}</t>
+          <t>IT</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'engineering'}</t>
+          <t>engineering</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Engineering'}</t>
+          <t>Engineering</t>
         </is>
       </c>
     </row>
@@ -950,12 +950,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'team_member'}</t>
+          <t>team_member</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Team member'}</t>
+          <t>Team member</t>
         </is>
       </c>
     </row>
@@ -967,12 +967,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -984,12 +984,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'stakeholder'}</t>
+          <t>stakeholder</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Stakeholder'}</t>
+          <t>Stakeholder</t>
         </is>
       </c>
     </row>
@@ -1001,12 +1001,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'office'}</t>
+          <t>office</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Office'}</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'remote'}</t>
+          <t>remote</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Remote'}</t>
+          <t>Remote</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
